--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
@@ -5170,13 +5170,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4194AD9-61CF-43F3-A094-210B0BCFD6D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CEEBE33-E87A-4E4D-95CB-BFFF86196864}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D56396-6674-4EBC-98B1-51D4F31A96F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{520CE9A9-280A-409F-BD8F-4C7203925B28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29DDC195-3CF1-490A-8C56-22E8F3607424}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E8F40B6-729E-43BD-B696-2DB39ADF01D8}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
@@ -5170,13 +5170,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CEEBE33-E87A-4E4D-95CB-BFFF86196864}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DC8C693-CBAA-47B5-A704-91831DDAA9CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{520CE9A9-280A-409F-BD8F-4C7203925B28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316297D0-52DF-4832-8C46-830EDB2B4563}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E8F40B6-729E-43BD-B696-2DB39ADF01D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1DFC69-4BFE-43E3-AA85-0E492B9FC147}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152514.xlsx
@@ -5170,13 +5170,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DC8C693-CBAA-47B5-A704-91831DDAA9CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4194AD9-61CF-43F3-A094-210B0BCFD6D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316297D0-52DF-4832-8C46-830EDB2B4563}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D56396-6674-4EBC-98B1-51D4F31A96F2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE1DFC69-4BFE-43E3-AA85-0E492B9FC147}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29DDC195-3CF1-490A-8C56-22E8F3607424}"/>
 </file>